--- a/artfynd/A 60753-2023 artfynd.xlsx
+++ b/artfynd/A 60753-2023 artfynd.xlsx
@@ -5322,10 +5322,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117617165</v>
+        <v>117611580</v>
       </c>
       <c r="B38" t="n">
-        <v>79428</v>
+        <v>74583</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5338,40 +5338,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>385</v>
+        <v>492</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sörstrand, Jmt</t>
+          <t>Björntjärnen (Björntjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509208</v>
+        <v>508671</v>
       </c>
       <c r="R38" t="n">
-        <v>7116540</v>
+        <v>7116744</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5409,7 +5406,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5428,7 +5424,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117611580</v>
+        <v>117610808</v>
       </c>
       <c r="B39" t="n">
         <v>74583</v>
@@ -5464,14 +5460,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Björntjärnen (Björntjärnen), Jmt</t>
+          <t>Sörstrand (Sörstrand), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508671</v>
+        <v>508693</v>
       </c>
       <c r="R39" t="n">
-        <v>7116744</v>
+        <v>7116702</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -5530,10 +5526,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117612544</v>
+        <v>117617165</v>
       </c>
       <c r="B40" t="n">
-        <v>90841</v>
+        <v>79428</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5546,37 +5542,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2062</v>
+        <v>385</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sörstrand (Sörstrand), Jmt</t>
+          <t>Sörstrand, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509185</v>
+        <v>509208</v>
       </c>
       <c r="R40" t="n">
-        <v>7116664</v>
+        <v>7116540</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5614,6 +5613,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5632,10 +5632,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117610808</v>
+        <v>117612544</v>
       </c>
       <c r="B41" t="n">
-        <v>74583</v>
+        <v>90841</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>492</v>
+        <v>2062</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508693</v>
+        <v>509185</v>
       </c>
       <c r="R41" t="n">
-        <v>7116702</v>
+        <v>7116664</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>

--- a/artfynd/A 60753-2023 artfynd.xlsx
+++ b/artfynd/A 60753-2023 artfynd.xlsx
@@ -5220,10 +5220,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117609983</v>
+        <v>117617165</v>
       </c>
       <c r="B37" t="n">
-        <v>78643</v>
+        <v>79430</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5236,34 +5236,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1249</v>
+        <v>385</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sörstrand (Sörstrand), Jmt</t>
+          <t>Sörstrand, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508993</v>
+        <v>509208</v>
       </c>
       <c r="R37" t="n">
-        <v>7116621</v>
+        <v>7116540</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -5304,6 +5307,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5322,10 +5326,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117611580</v>
+        <v>117612544</v>
       </c>
       <c r="B38" t="n">
-        <v>74583</v>
+        <v>90843</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5338,34 +5342,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>492</v>
+        <v>2062</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Björntjärnen (Björntjärnen), Jmt</t>
+          <t>Sörstrand (Sörstrand), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508671</v>
+        <v>509185</v>
       </c>
       <c r="R38" t="n">
-        <v>7116744</v>
+        <v>7116664</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -5424,10 +5428,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117610808</v>
+        <v>117609983</v>
       </c>
       <c r="B39" t="n">
-        <v>74583</v>
+        <v>78645</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5440,21 +5444,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>492</v>
+        <v>1249</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5464,13 +5468,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508693</v>
+        <v>508993</v>
       </c>
       <c r="R39" t="n">
-        <v>7116702</v>
+        <v>7116621</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5526,10 +5530,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117617165</v>
+        <v>117610808</v>
       </c>
       <c r="B40" t="n">
-        <v>79428</v>
+        <v>74585</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5542,40 +5546,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>385</v>
+        <v>492</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sörstrand, Jmt</t>
+          <t>Sörstrand (Sörstrand), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509208</v>
+        <v>508693</v>
       </c>
       <c r="R40" t="n">
-        <v>7116540</v>
+        <v>7116702</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5613,7 +5614,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5632,10 +5632,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117612544</v>
+        <v>117611580</v>
       </c>
       <c r="B41" t="n">
-        <v>90841</v>
+        <v>74585</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5648,34 +5648,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2062</v>
+        <v>492</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sörstrand (Sörstrand), Jmt</t>
+          <t>Björntjärnen (Björntjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509185</v>
+        <v>508671</v>
       </c>
       <c r="R41" t="n">
-        <v>7116664</v>
+        <v>7116744</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5737,7 +5737,7 @@
         <v>117610915</v>
       </c>
       <c r="B42" t="n">
-        <v>79427</v>
+        <v>79429</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 60753-2023 artfynd.xlsx
+++ b/artfynd/A 60753-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5834,6 +5834,6194 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120516834</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>508649</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7116442</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120524001</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>508681</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7116559</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120512612</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90591</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>508728</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7116843</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120522950</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>508777</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7116883</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120511480</v>
+      </c>
+      <c r="B47" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>508732</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7116976</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120511408</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>508723</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7116950</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120515957</v>
+      </c>
+      <c r="B49" t="n">
+        <v>56532</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>508673</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7116412</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120523991</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>508617</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7116681</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120516207</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>508634</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7116363</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120523987</v>
+      </c>
+      <c r="B52" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>508645</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7116655</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120523995</v>
+      </c>
+      <c r="B53" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>658</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>508644</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7116464</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120511819</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>508751</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7116877</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120511265</v>
+      </c>
+      <c r="B55" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>508710</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7116959</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120511472</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>508723</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7116954</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120512712</v>
+      </c>
+      <c r="B57" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>508711</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7116867</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120513199</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>508618</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7116880</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120516723</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>508638</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7116441</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120516628</v>
+      </c>
+      <c r="B60" t="n">
+        <v>90545</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>508618</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7116441</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120514401</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>508598</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7116745</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120512579</v>
+      </c>
+      <c r="B62" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>508733</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7116829</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120513584</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>508580</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7116858</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120524003</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>508622</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7116708</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120512516</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>508750</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7116834</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120522922</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>508762</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7116833</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120512351</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>508800</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7116854</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120523994</v>
+      </c>
+      <c r="B68" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>658</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>508546</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7116588</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120511072</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>508699</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7116971</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120511107</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>508700</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7116978</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120516386</v>
+      </c>
+      <c r="B71" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>508633</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7116362</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120523996</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>508631</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7116630</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På sälg och gran</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120523999</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>508660</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7116610</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120513421</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>508575</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7116857</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120514253</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>508588</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7116709</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120511503</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>508735</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7116951</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120511970</v>
+      </c>
+      <c r="B77" t="n">
+        <v>90545</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>508750</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7116891</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120510830</v>
+      </c>
+      <c r="B78" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>508698</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7116972</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120522935</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79659</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>508569</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7116743</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120523990</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>508626</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7116498</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120510804</v>
+      </c>
+      <c r="B81" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>658</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>508699</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7116978</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120516438</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>508642</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7116388</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120522906</v>
+      </c>
+      <c r="B83" t="n">
+        <v>90591</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>508675</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7116781</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120524000</v>
+      </c>
+      <c r="B84" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>508630</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7116625</v>
+      </c>
+      <c r="S84" t="n">
+        <v>25</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120523997</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>508555</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7116587</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120524004</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91146</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>760</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>508631</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7116630</v>
+      </c>
+      <c r="S86" t="n">
+        <v>25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>120522938</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>508569</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7116743</v>
+      </c>
+      <c r="S87" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>120522875</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>508561</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7116637</v>
+      </c>
+      <c r="S88" t="n">
+        <v>25</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>120522893</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>508675</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7116781</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120516045</v>
+      </c>
+      <c r="B90" t="n">
+        <v>90351</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>508687</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7116375</v>
+      </c>
+      <c r="S90" t="n">
+        <v>15</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120513163</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>508630</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7116883</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120523992</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>508596</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7116687</v>
+      </c>
+      <c r="S92" t="n">
+        <v>25</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120523988</v>
+      </c>
+      <c r="B93" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>508621</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7116687</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120513727</v>
+      </c>
+      <c r="B94" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>508587</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7116847</v>
+      </c>
+      <c r="S94" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>120516599</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>508623</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7116428</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>120511668</v>
+      </c>
+      <c r="B96" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>508748</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7116942</v>
+      </c>
+      <c r="S96" t="n">
+        <v>15</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>120515917</v>
+      </c>
+      <c r="B97" t="n">
+        <v>90972</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>508692</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7116426</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>120512491</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>508757</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7116839</v>
+      </c>
+      <c r="S98" t="n">
+        <v>15</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>120515598</v>
+      </c>
+      <c r="B99" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>658</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>508677</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7116643</v>
+      </c>
+      <c r="S99" t="n">
+        <v>15</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>120523993</v>
+      </c>
+      <c r="B100" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>508594</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7116517</v>
+      </c>
+      <c r="S100" t="n">
+        <v>25</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>120511731</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Skärviken, Skärviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>508773</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7116904</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>120523998</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Sörstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>508654</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7116475</v>
+      </c>
+      <c r="S102" t="n">
+        <v>25</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60753-2023 artfynd.xlsx
+++ b/artfynd/A 60753-2023 artfynd.xlsx
@@ -37079,7 +37079,7 @@
         <v>120536370</v>
       </c>
       <c r="B347" t="n">
-        <v>90880</v>
+        <v>90890</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>

--- a/artfynd/A 60753-2023 artfynd.xlsx
+++ b/artfynd/A 60753-2023 artfynd.xlsx
@@ -37079,7 +37079,7 @@
         <v>120536370</v>
       </c>
       <c r="B347" t="n">
-        <v>90890</v>
+        <v>90902</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>

--- a/artfynd/A 60753-2023 artfynd.xlsx
+++ b/artfynd/A 60753-2023 artfynd.xlsx
@@ -37079,7 +37079,7 @@
         <v>120536370</v>
       </c>
       <c r="B347" t="n">
-        <v>90902</v>
+        <v>90903</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>

--- a/artfynd/A 60753-2023 artfynd.xlsx
+++ b/artfynd/A 60753-2023 artfynd.xlsx
@@ -37079,7 +37079,7 @@
         <v>120536370</v>
       </c>
       <c r="B347" t="n">
-        <v>90903</v>
+        <v>90906</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>

--- a/artfynd/A 60753-2023 artfynd.xlsx
+++ b/artfynd/A 60753-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY340"/>
+  <dimension ref="A1:AZ340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536370</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539841</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591064</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591085</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591086</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591087</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117617165</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117610915</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117610808</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117611580</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533285</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591152</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120510804</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120515598</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523994</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523995</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2325,6 +2410,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536385</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2422,6 +2512,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539867</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2519,6 +2614,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539868</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2616,6 +2716,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539869</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2713,6 +2818,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591097</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2810,6 +2920,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591099</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2907,6 +3022,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591100</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3004,6 +3124,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591102</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3101,6 +3226,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591104</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3198,6 +3328,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591105</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3295,6 +3430,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596148</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3392,6 +3532,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120598293</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3489,6 +3634,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120613148</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3586,6 +3736,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632337</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3683,6 +3838,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632338</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3780,6 +3940,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632339</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3877,6 +4042,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632340</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3974,6 +4144,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632341</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4071,6 +4246,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632342</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4168,6 +4348,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120524004</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4265,6 +4450,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120549934</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4362,6 +4552,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120605882</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4459,6 +4654,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539911</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4556,6 +4756,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591144</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4653,6 +4858,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591145</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4750,6 +4960,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632384</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4847,6 +5062,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120510830</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4944,6 +5164,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511265</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5041,6 +5266,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511480</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5138,6 +5368,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120512712</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5235,6 +5470,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513727</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5332,6 +5572,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523987</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5429,6 +5674,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523988</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5526,6 +5776,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536017</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5623,6 +5878,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539843</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5720,6 +5980,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539844</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5817,6 +6082,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120546941</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5914,6 +6184,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120552941</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6011,6 +6286,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591066</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6108,6 +6388,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591067</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6205,6 +6490,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591068</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6302,6 +6592,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591069</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6399,6 +6694,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591070</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6496,6 +6796,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591071</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6593,6 +6898,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591072</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6690,6 +7000,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591073</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6787,6 +7102,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591074</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6884,6 +7204,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595924</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6981,6 +7306,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596266</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7078,6 +7408,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596939</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7175,6 +7510,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120611047</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7272,6 +7612,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632317</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7369,6 +7714,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632318</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7466,6 +7816,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632319</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7563,6 +7918,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632320</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7660,6 +8020,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120512612</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7761,6 +8126,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522906</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7858,6 +8228,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591084</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7955,6 +8330,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511408</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8052,6 +8432,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511503</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8149,6 +8534,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511668</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8246,6 +8636,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513584</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8343,6 +8738,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120516834</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8440,6 +8840,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523993</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8537,6 +8942,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530870</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8634,6 +9044,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539863</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8731,6 +9146,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553600</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8828,6 +9248,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591089</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8925,6 +9350,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591090</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9022,6 +9452,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591091</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9119,6 +9554,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591092</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9216,6 +9656,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591093</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9313,6 +9758,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591094</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9410,6 +9860,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591095</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9507,6 +9962,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591096</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9604,6 +10064,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595988</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9701,6 +10166,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596584</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9798,6 +10268,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618606</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9895,6 +10370,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632332</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9992,6 +10472,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632333</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10089,6 +10574,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632334</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10186,6 +10676,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632335</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10283,6 +10778,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632336</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10380,6 +10880,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117609983</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10477,6 +10982,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117612544</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10574,6 +11084,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539842</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10671,6 +11186,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591065</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10787,6 +11307,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900813</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10903,6 +11428,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900883</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11019,6 +11549,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900886</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11135,6 +11670,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900899</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11249,6 +11789,11 @@
       <c r="AY109" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90901959</t>
         </is>
       </c>
     </row>
@@ -11352,6 +11897,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522938</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11449,6 +11999,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523991</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11546,6 +12101,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523992</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11648,6 +12208,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120529044</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11750,6 +12315,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539855</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11847,6 +12417,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539856</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11944,6 +12519,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539857</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12041,6 +12621,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539858</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12138,6 +12723,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539859</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12235,6 +12825,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539861</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12332,6 +12927,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539862</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12429,6 +13029,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120552296</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12526,6 +13131,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591088</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12623,6 +13233,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120516045</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12720,6 +13335,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591076</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12817,6 +13437,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591077</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12914,6 +13539,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591078</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13025,6 +13655,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900664</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13136,6 +13771,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900665</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13247,6 +13887,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900890</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13344,6 +13989,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591083</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13441,6 +14091,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511970</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13538,6 +14193,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120516628</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13635,6 +14295,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632316</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13732,6 +14397,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511687</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13829,6 +14499,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120514253</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13926,6 +14601,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120524001</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14023,6 +14703,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120524003</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14120,6 +14805,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120529124</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14217,6 +14907,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533261</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14319,6 +15014,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539918</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14416,6 +15116,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539919</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14513,6 +15218,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539920</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14610,6 +15320,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539921</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14707,6 +15422,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539922</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14804,6 +15524,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539923</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14901,6 +15626,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591151</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14998,6 +15728,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632388</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15114,6 +15849,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900770</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15230,6 +15970,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900759</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15346,6 +16091,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900772</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15462,6 +16212,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900776</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15578,6 +16333,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900810</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15694,6 +16454,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900814</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15810,6 +16575,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900819</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15926,6 +16696,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900882</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16042,6 +16817,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900885</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16158,6 +16938,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900887</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16274,6 +17059,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900892</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16390,6 +17180,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900896</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16506,6 +17301,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900898</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16622,6 +17422,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90901960</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16719,6 +17524,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511072</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16816,6 +17626,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511731</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16918,6 +17733,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511819</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17015,6 +17835,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120512351</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17112,6 +17937,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513163</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17209,6 +18039,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513199</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17310,6 +18145,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522893</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17411,6 +18251,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522922</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17513,6 +18358,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523996</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17610,6 +18460,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523997</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17707,6 +18562,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523998</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17804,6 +18664,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523999</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17906,6 +18771,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120529051</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18003,6 +18873,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120534281</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18100,6 +18975,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120534334</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18202,6 +19082,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539870</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18304,6 +19189,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539871</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18401,6 +19291,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539872</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18498,6 +19393,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539873</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18595,6 +19495,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539874</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18692,6 +19597,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539875</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18789,6 +19699,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539876</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18886,6 +19801,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539877</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18983,6 +19903,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539878</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19080,6 +20005,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539879</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19177,6 +20107,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539880</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19274,6 +20209,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539882</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19371,6 +20311,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539883</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19468,6 +20413,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539884</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19565,6 +20515,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539885</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19662,6 +20617,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539886</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19759,6 +20719,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539887</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19856,6 +20821,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539888</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19953,6 +20923,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539889</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20050,6 +21025,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120552292</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20147,6 +21127,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553450</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20244,6 +21229,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553536</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20346,6 +21336,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591107</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20448,6 +21443,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591109</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20550,6 +21550,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591110</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20652,6 +21657,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591111</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20749,6 +21759,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591113</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20846,6 +21861,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591114</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20943,6 +21963,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591115</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21040,6 +22065,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591116</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21137,6 +22167,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591117</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21234,6 +22269,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591118</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21331,6 +22371,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591119</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21428,6 +22473,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591120</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21525,6 +22575,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591121</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21622,6 +22677,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591122</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21719,6 +22779,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591123</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21816,6 +22881,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591125</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21913,6 +22983,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596045</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22010,6 +23085,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596138</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22107,6 +23187,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596983</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22204,6 +23289,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120602074</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22301,6 +23391,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120610728</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22398,6 +23493,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617963</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22495,6 +23595,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120624424</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22597,6 +23702,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632343</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22699,6 +23809,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632344</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22801,6 +23916,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632345</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22903,6 +24023,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632346</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23005,6 +24130,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632347</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23107,6 +24237,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632348</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23204,6 +24339,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632357</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23301,6 +24441,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632358</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23398,6 +24543,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632360</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23495,6 +24645,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632361</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23592,6 +24747,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632362</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23689,6 +24849,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632363</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23805,6 +24970,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900884</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23921,6 +25091,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90901957</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24018,6 +25193,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511107</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24115,6 +25295,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539852</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24212,6 +25397,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539853</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24309,6 +25499,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539854</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24406,6 +25601,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632327</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24522,6 +25722,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900771</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24638,6 +25843,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900812</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24754,6 +25964,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900895</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24870,6 +26085,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900897</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -24986,6 +26206,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90901958</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -25083,6 +26308,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511085</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25184,6 +26414,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522935</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25286,6 +26521,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591127</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25383,6 +26623,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591128</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25480,6 +26725,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632364</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25582,6 +26832,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513421</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25689,6 +26944,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120510764</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25791,6 +27051,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120514401</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25898,6 +27163,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120516599</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -26000,6 +27270,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539845</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -26102,6 +27377,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539846</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -26204,6 +27484,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539847</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26306,6 +27591,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551658</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26408,6 +27698,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120552760</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26510,6 +27805,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553628</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26607,6 +27907,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120515957</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26713,6 +28018,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591142</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26815,6 +28125,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120550361</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -26917,6 +28232,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120512516</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -27022,6 +28342,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522875</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -27124,6 +28449,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523990</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27226,6 +28556,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539849</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27328,6 +28663,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539851</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -27430,6 +28770,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591082</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27532,6 +28877,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632324</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -27634,6 +28984,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632325</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -27736,6 +29091,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632326</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -27847,6 +29207,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132696</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -27958,6 +29323,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132702</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -28055,6 +29425,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120516386</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -28152,6 +29527,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120516475</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -28254,6 +29634,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522950</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -28351,6 +29736,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120529075</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -28448,6 +29838,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120529107</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28545,6 +29940,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530179</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -28642,6 +30042,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120532891</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -28739,6 +30144,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120534181</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -28836,6 +30246,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120534847</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -28938,6 +30353,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539891</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -29035,6 +30455,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539892</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -29132,6 +30557,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539893</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -29229,6 +30659,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539896</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -29326,6 +30761,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539897</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -29423,6 +30863,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539898</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -29520,6 +30965,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539899</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -29617,6 +31067,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539901</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -29714,6 +31169,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539902</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -29811,6 +31271,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539903</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -29908,6 +31373,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539904</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -30005,6 +31475,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539906</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -30102,6 +31577,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539907</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -30199,6 +31679,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539908</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -30296,6 +31781,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539909</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -30393,6 +31883,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120539910</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -30490,6 +31985,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120547204</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -30587,6 +32087,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551031</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -30684,6 +32189,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551179</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -30781,6 +32291,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551277</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -30878,6 +32393,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551448</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -30975,6 +32495,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120552493</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -31072,6 +32597,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120552585</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -31169,6 +32699,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553357</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -31271,6 +32806,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553726</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -31368,6 +32908,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553760</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -31470,6 +33015,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120554037</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -31567,6 +33117,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120558944</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -31664,6 +33219,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591130</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -31761,6 +33321,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591135</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -31858,6 +33423,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591136</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -31955,6 +33525,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591137</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -32052,6 +33627,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591138</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -32149,6 +33729,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591139</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -32246,6 +33831,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596225</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -32343,6 +33933,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596566</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -32440,6 +34035,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596710</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -32537,6 +34137,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596915</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -32634,6 +34239,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120610520</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -32731,6 +34341,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120615306</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -32828,6 +34443,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617582</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -32925,6 +34545,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617618</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -33022,6 +34647,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617893</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -33119,6 +34749,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618388</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -33216,6 +34851,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618780</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -33313,6 +34953,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632376</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -33410,6 +35055,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632378</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -33507,6 +35157,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120591106</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -33618,6 +35273,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132687</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -33729,6 +35389,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132674</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -33840,6 +35505,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132688</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -33956,6 +35626,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900894</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -34053,6 +35728,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632369</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -34150,6 +35830,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120515917</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -34247,6 +35932,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632366</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -34344,6 +36034,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595978</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -34441,8 +36136,354 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596284</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>